--- a/docs/eduai-excel-gantt-complex.xlsx
+++ b/docs/eduai-excel-gantt-complex.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView windowWidth="20752" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="WBS-Level Gantt" sheetId="2" r:id="rId1"/>
@@ -434,7 +434,7 @@
     <t>4.10</t>
   </si>
   <si>
-    <t>资源删除 / 重试 / 下载</t>
+    <t>资源删除 / 下载</t>
   </si>
   <si>
     <t>4.11</t>
@@ -620,13 +620,13 @@
     <t>教学闭环完成</t>
   </si>
   <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>全功能集成完成</t>
+  </si>
+  <si>
     <t>计划中</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>全功能集成完成</t>
   </si>
   <si>
     <t>M5</t>
@@ -6086,7 +6086,7 @@
         <v>46152</v>
       </c>
       <c r="E43" s="5">
-        <v>46166</v>
+        <v>46180</v>
       </c>
       <c r="F43" s="2">
         <v>6</v>
@@ -6147,20 +6147,20 @@
       <c r="BH43" s="8"/>
       <c r="BI43" s="8"/>
       <c r="BJ43" s="8"/>
-      <c r="BK43" s="2"/>
-      <c r="BL43" s="2"/>
-      <c r="BM43" s="2"/>
-      <c r="BN43" s="2"/>
-      <c r="BO43" s="2"/>
-      <c r="BP43" s="9"/>
-      <c r="BQ43" s="9"/>
-      <c r="BR43" s="2"/>
-      <c r="BS43" s="2"/>
-      <c r="BT43" s="2"/>
-      <c r="BU43" s="2"/>
-      <c r="BV43" s="2"/>
-      <c r="BW43" s="9"/>
-      <c r="BX43" s="9"/>
+      <c r="BK43" s="8"/>
+      <c r="BL43" s="8"/>
+      <c r="BM43" s="8"/>
+      <c r="BN43" s="8"/>
+      <c r="BO43" s="8"/>
+      <c r="BP43" s="8"/>
+      <c r="BQ43" s="8"/>
+      <c r="BR43" s="8"/>
+      <c r="BS43" s="8"/>
+      <c r="BT43" s="8"/>
+      <c r="BU43" s="8"/>
+      <c r="BV43" s="8"/>
+      <c r="BW43" s="8"/>
+      <c r="BX43" s="8"/>
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
       <c r="CA43" s="2"/>
@@ -6657,10 +6657,10 @@
         <v>86</v>
       </c>
       <c r="D49" s="5">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>187</v>
@@ -6713,16 +6713,16 @@
       <c r="AZ49" s="2"/>
       <c r="BA49" s="2"/>
       <c r="BB49" s="9"/>
-      <c r="BC49" s="10" t="s">
-        <v>191</v>
-      </c>
+      <c r="BC49" s="9"/>
       <c r="BD49" s="2"/>
       <c r="BE49" s="2"/>
       <c r="BF49" s="2"/>
       <c r="BG49" s="2"/>
       <c r="BH49" s="2"/>
       <c r="BI49" s="9"/>
-      <c r="BJ49" s="9"/>
+      <c r="BJ49" s="10" t="s">
+        <v>191</v>
+      </c>
       <c r="BK49" s="2"/>
       <c r="BL49" s="2"/>
       <c r="BM49" s="2"/>
@@ -6747,19 +6747,19 @@
     </row>
     <row r="50" spans="1:83">
       <c r="A50" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D50" s="5">
-        <v>46173</v>
+        <v>46180</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>187</v>
@@ -6826,16 +6826,16 @@
       <c r="BN50" s="2"/>
       <c r="BO50" s="2"/>
       <c r="BP50" s="9"/>
-      <c r="BQ50" s="10" t="s">
-        <v>191</v>
-      </c>
+      <c r="BQ50" s="9"/>
       <c r="BR50" s="2"/>
       <c r="BS50" s="2"/>
       <c r="BT50" s="2"/>
       <c r="BU50" s="2"/>
       <c r="BV50" s="2"/>
       <c r="BW50" s="9"/>
-      <c r="BX50" s="9"/>
+      <c r="BX50" s="10" t="s">
+        <v>191</v>
+      </c>
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
       <c r="CA50" s="2"/>
@@ -6858,7 +6858,7 @@
         <v>46187</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>187</v>
@@ -7019,21 +7019,21 @@
         <v>46159</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="C5" s="5">
         <v>46173</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7047,7 +7047,7 @@
         <v>46187</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
